--- a/docs/build/lakeshore-enterprise-context/source/10_vendors_contracts_source/bafo_model.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/10_vendors_contracts_source/bafo_model.xlsx
@@ -478,14 +478,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40</v>
+        <v>26.7</v>
       </c>
       <c r="C3" t="n">
-        <v>32.1</v>
+        <v>11.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>5.5%</t>
         </is>
       </c>
     </row>
@@ -496,14 +496,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.6</v>
+        <v>8.5</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>14.7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>5.1%</t>
         </is>
       </c>
     </row>
@@ -514,14 +514,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.3</v>
+        <v>37.1</v>
       </c>
       <c r="C5" t="n">
-        <v>8.6</v>
+        <v>26</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>13.7%</t>
         </is>
       </c>
     </row>
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>15.1</v>
+        <v>10.1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38.9</v>
+        <v>25</v>
       </c>
       <c r="C7" t="n">
-        <v>21.4</v>
+        <v>29.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>20.9%</t>
         </is>
       </c>
     </row>
